--- a/Work-Log-0626.xlsx
+++ b/Work-Log-0626.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Create Export function in Person &amp; Company page of CRM</t>
   </si>
@@ -38,7 +38,38 @@
     <t>Tracked Hrs</t>
   </si>
   <si>
-    <t>Total: 7Hrs</t>
+    <t>2026.07.02-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-fill contact fields when using + RFI from a project
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default Prepared By / By Company + “Remember as my default”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send to Client email draft improvements (CC, signature, attach reminder, no false sent date)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove RFI_ from PDF filename
+</t>
+  </si>
+  <si>
+    <t>Total: 8 hrs/ 280AUD</t>
+  </si>
+  <si>
+    <t>2026.06.25</t>
+  </si>
+  <si>
+    <t>Total: 7 hrs/ 245AUD</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Tasks</t>
   </si>
 </sst>
 </file>
@@ -74,8 +105,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -356,57 +402,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="77.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>4</v>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Work-Log-0626.xlsx
+++ b/Work-Log-0626.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Create Export function in Person &amp; Company page of CRM</t>
   </si>
@@ -70,6 +70,57 @@
   </si>
   <si>
     <t>Tasks</t>
+  </si>
+  <si>
+    <t>Analyse existing manual import + design the automation architecture</t>
+  </si>
+  <si>
+    <t>Verify Time Doctor API live (login, company, projects, worklog tests)</t>
+  </si>
+  <si>
+    <t>Provision Azure (resource group, Key Vault + secrets, Function App, App Insights, provider registration)</t>
+  </si>
+  <si>
+    <t>Entra app registration + first admin-consent setup</t>
+  </si>
+  <si>
+    <t>Build the sync Function (TD client, Graph client, matching port, idempotent TimeLog design, safety guards, timer + manual trigger)</t>
+  </si>
+  <si>
+    <t>Deploy + first cloud dry-run and verification</t>
+  </si>
+  <si>
+    <t>Setup Helper app for site permission + consent coordination with client</t>
+  </si>
+  <si>
+    <t>Diagnose &amp; fix AADSTS500113 consent error (redirect URI)</t>
+  </si>
+  <si>
+    <t>Site permission grant + helper cleanup</t>
+  </si>
+  <si>
+    <t>Full end-to-end dry-run + version-history double-count analysis</t>
+  </si>
+  <si>
+    <t>Go-live cutover (baseline column, 54 snapshots, first live sync, verification)</t>
+  </si>
+  <si>
+    <t>Replace manual import buttons with auto-sync status chip (manager + staff)</t>
+  </si>
+  <si>
+    <t>Quote follow-up date (modal field + main-sheet display + new list column)</t>
+  </si>
+  <si>
+    <t>Dated notes insert (date picker + add button in Notes)</t>
+  </si>
+  <si>
+    <t>Rebuild, test, package .sppkg for deployment</t>
+  </si>
+  <si>
+    <t>2026.07.20-29</t>
+  </si>
+  <si>
+    <t>Total: 28 hrs/ 980AUD</t>
   </si>
 </sst>
 </file>
@@ -402,16 +453,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="77.42578125" customWidth="1"/>
+    <col min="2" max="2" width="114.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -422,7 +473,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -433,7 +484,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="5"/>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -442,7 +493,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -451,19 +502,19 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -474,7 +525,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
@@ -483,7 +534,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -492,7 +543,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
@@ -501,16 +552,160 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="5"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A13:A28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
